--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\python\pythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB22C55-C29B-4497-8119-85FFA423DD05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8024EC7B-9786-404B-BF97-CF8324930BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{E6B9EE15-1050-48D8-946F-E1029E1F1852}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -130,17 +130,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>data.access_token</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>/api/news/core-info/list</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>需要token</t>
-  </si>
-  <si>
     <t>快讯分页查询</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -158,6 +151,34 @@
   </si>
   <si>
     <t>{"authorization": "${token}"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>token:$.data.access_token</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ids:$.data.list[*].id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快讯详情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要token，需要快讯id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/news/queryNewsInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"newsId": "${ids[0]}"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -545,9 +566,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0E2704-9E56-4315-B469-7261CC411884}">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="4" max="4" width="21.9296875" customWidth="1"/>
     <col min="5" max="5" width="30.46484375" customWidth="1"/>
     <col min="7" max="7" width="92.9296875" customWidth="1"/>
     <col min="8" max="8" width="79.06640625" customWidth="1"/>
@@ -629,7 +651,7 @@
         <v>17</v>
       </c>
       <c r="M2" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
@@ -637,30 +659,65 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
         <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" t="s">
-        <v>28</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
       </c>
       <c r="I3" t="s">
         <v>16</v>
       </c>
       <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
         <v>17</v>
       </c>
     </row>

--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\python\pythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8024EC7B-9786-404B-BF97-CF8324930BD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBACBF29-312A-4740-A818-972ED4D45F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{E6B9EE15-1050-48D8-946F-E1029E1F1852}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -179,6 +179,10 @@
   </si>
   <si>
     <t>{"newsId": "${ids[0]}"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT * from news_flash where id=${ids[0]}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -569,12 +573,13 @@
   <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
+    <col min="3" max="3" width="18" customWidth="1"/>
     <col min="4" max="4" width="21.9296875" customWidth="1"/>
     <col min="5" max="5" width="30.46484375" customWidth="1"/>
     <col min="7" max="7" width="92.9296875" customWidth="1"/>
     <col min="8" max="8" width="79.06640625" customWidth="1"/>
     <col min="10" max="10" width="17.06640625" customWidth="1"/>
-    <col min="11" max="11" width="11.265625" customWidth="1"/>
+    <col min="11" max="11" width="41.86328125" customWidth="1"/>
     <col min="12" max="12" width="18.06640625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -720,6 +725,9 @@
       <c r="J4" t="s">
         <v>17</v>
       </c>
+      <c r="K4" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\python\pythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBACBF29-312A-4740-A818-972ED4D45F5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B8C444-1224-4066-B5EB-54DEBDE7C621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{E6B9EE15-1050-48D8-946F-E1029E1F1852}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -183,6 +183,10 @@
   </si>
   <si>
     <t>SELECT * from news_flash where id=${ids[0]}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>title=极智嘉通过港交所上市审核,status=2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -580,7 +584,7 @@
     <col min="8" max="8" width="79.06640625" customWidth="1"/>
     <col min="10" max="10" width="17.06640625" customWidth="1"/>
     <col min="11" max="11" width="41.86328125" customWidth="1"/>
-    <col min="12" max="12" width="18.06640625" customWidth="1"/>
+    <col min="12" max="12" width="39.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.4">
@@ -727,6 +731,9 @@
       </c>
       <c r="K4" t="s">
         <v>34</v>
+      </c>
+      <c r="L4" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\python\pythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54B8C444-1224-4066-B5EB-54DEBDE7C621}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1557964-15EE-4619-8237-D47BA705B38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{E6B9EE15-1050-48D8-946F-E1029E1F1852}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -182,11 +182,34 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SELECT * from news_flash where id=${ids[0]}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>title=极智嘉通过港交所上市审核,status=2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT * from news_flash where id=${ids[0]} </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>db_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实验下多链接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT * from content_activity where content_id ='77359212'</t>
+  </si>
+  <si>
+    <t>address_name=曼谷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>content</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -574,7 +597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB0E2704-9E56-4315-B469-7261CC411884}">
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="3" max="3" width="18" customWidth="1"/>
@@ -584,10 +607,11 @@
     <col min="8" max="8" width="79.06640625" customWidth="1"/>
     <col min="10" max="10" width="17.06640625" customWidth="1"/>
     <col min="11" max="11" width="41.86328125" customWidth="1"/>
-    <col min="12" max="12" width="39.6640625" customWidth="1"/>
+    <col min="12" max="12" width="26.1328125" customWidth="1"/>
+    <col min="13" max="13" width="27.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -627,8 +651,11 @@
       <c r="M1" t="s">
         <v>15</v>
       </c>
+      <c r="N1" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" ht="222" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:14" ht="222" x14ac:dyDescent="0.4">
       <c r="A2">
         <v>1</v>
       </c>
@@ -663,7 +690,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>2</v>
       </c>
@@ -698,7 +725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>3</v>
       </c>
@@ -730,10 +757,54 @@
         <v>17</v>
       </c>
       <c r="K4" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" t="s">
         <v>34</v>
       </c>
-      <c r="L4" t="s">
-        <v>35</v>
+      <c r="N4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" t="s">
+        <v>40</v>
+      </c>
+      <c r="N5" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\python\pythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1557964-15EE-4619-8237-D47BA705B38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E8EE93-D2B2-45C6-810E-309C2D4AC9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{E6B9EE15-1050-48D8-946F-E1029E1F1852}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -146,70 +146,86 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>{"authorization": "${token}"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>token:$.data.access_token</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ids:$.data.list[*].id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>快讯详情</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>需要token，需要快讯id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>/api/news/queryNewsInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>POST</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"newsId": "${ids[0]}"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>title=极智嘉通过港交所上市审核,status=2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SELECT * from news_flash where id=${ids[0]} </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>db_name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>实验下多链接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SELECT * from content_activity where content_id ='77359212'</t>
+  </si>
+  <si>
+    <t>address_name=曼谷</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>content</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>{"pageNo":1,"pageSize":10}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"authorization": "${token}"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>token:$.data.access_token</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ids:$.data.list[*].id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>快讯详情</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>需要token，需要快讯id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>/api/news/queryNewsInfo</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>POST</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"newsId": "${ids[0]}"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>title=极智嘉通过港交所上市审核,status=2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">SELECT * from news_flash where id=${ids[0]} </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>db_name</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>实验下多链接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SELECT * from content_activity where content_id ='77359212'</t>
-  </si>
-  <si>
-    <t>address_name=曼谷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>content</t>
+    <t>成功,21215</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>msg,data.total</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>number=2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select count(*) as number from news_flash where publish_time between '2026-05-23 00:00:00' and '2026-05-23 23:59:59'</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -604,10 +620,11 @@
     <col min="4" max="4" width="21.9296875" customWidth="1"/>
     <col min="5" max="5" width="30.46484375" customWidth="1"/>
     <col min="7" max="7" width="92.9296875" customWidth="1"/>
-    <col min="8" max="8" width="79.06640625" customWidth="1"/>
+    <col min="8" max="8" width="95.265625" customWidth="1"/>
+    <col min="9" max="9" width="13.53125" customWidth="1"/>
     <col min="10" max="10" width="17.06640625" customWidth="1"/>
-    <col min="11" max="11" width="41.86328125" customWidth="1"/>
-    <col min="12" max="12" width="26.1328125" customWidth="1"/>
+    <col min="11" max="11" width="72" customWidth="1"/>
+    <col min="12" max="12" width="50.796875" customWidth="1"/>
     <col min="13" max="13" width="27.86328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -652,7 +669,7 @@
         <v>15</v>
       </c>
       <c r="N1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="222" x14ac:dyDescent="0.4">
@@ -687,7 +704,7 @@
         <v>17</v>
       </c>
       <c r="M2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.4">
@@ -710,19 +727,28 @@
         <v>24</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="J3" t="s">
-        <v>17</v>
+        <v>43</v>
+      </c>
+      <c r="K3" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" t="s">
+        <v>44</v>
       </c>
       <c r="M3" t="s">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="N3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -730,25 +756,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" t="s">
         <v>29</v>
       </c>
-      <c r="C4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>31</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" t="s">
         <v>32</v>
-      </c>
-      <c r="G4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>33</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
@@ -757,39 +783,39 @@
         <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="L4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="N4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
         <v>29</v>
       </c>
-      <c r="C5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>30</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>31</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
+        <v>25</v>
+      </c>
+      <c r="H5" t="s">
         <v>32</v>
-      </c>
-      <c r="G5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
       </c>
       <c r="I5" t="s">
         <v>16</v>
@@ -798,13 +824,13 @@
         <v>17</v>
       </c>
       <c r="K5" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" t="s">
         <v>39</v>
       </c>
-      <c r="L5" t="s">
+      <c r="N5" t="s">
         <v>40</v>
-      </c>
-      <c r="N5" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\python\pythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E8EE93-D2B2-45C6-810E-309C2D4AC9B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D8D3FB-3D08-40FD-B560-54DA0ABA3925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{E6B9EE15-1050-48D8-946F-E1029E1F1852}"/>
   </bookViews>
@@ -209,11 +209,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{"pageNo":1,"pageSize":10}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>成功,21215</t>
+    <t>成功,2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -225,7 +221,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>select count(*) as number from news_flash where publish_time between '2026-05-23 00:00:00' and '2026-05-23 23:59:59'</t>
+    <t>select * from news_flash where publish_time between '2026-05-23 00:00:00' and '2026-05-23 23:59:59'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"pageNo": 1,"pageSize": 10,"startTime": "2026-05-23 00:00:00","endTime": "2026-05-23 23:59:59"}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -623,7 +623,7 @@
     <col min="8" max="8" width="95.265625" customWidth="1"/>
     <col min="9" max="9" width="13.53125" customWidth="1"/>
     <col min="10" max="10" width="17.06640625" customWidth="1"/>
-    <col min="11" max="11" width="72" customWidth="1"/>
+    <col min="11" max="11" width="84.6640625" customWidth="1"/>
     <col min="12" max="12" width="50.796875" customWidth="1"/>
     <col min="13" max="13" width="27.86328125" customWidth="1"/>
   </cols>
@@ -730,19 +730,19 @@
         <v>25</v>
       </c>
       <c r="H3" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" t="s">
         <v>41</v>
       </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
         <v>42</v>
       </c>
-      <c r="J3" t="s">
+      <c r="K3" t="s">
+        <v>44</v>
+      </c>
+      <c r="L3" t="s">
         <v>43</v>
-      </c>
-      <c r="K3" t="s">
-        <v>45</v>
-      </c>
-      <c r="L3" t="s">
-        <v>44</v>
       </c>
       <c r="M3" t="s">
         <v>27</v>

--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\python\pythonProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1D8D3FB-3D08-40FD-B560-54DA0ABA3925}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1363639D-1055-46F1-9F06-77A16B8EE993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="23236" windowHeight="13875" xr2:uid="{E6B9EE15-1050-48D8-946F-E1029E1F1852}"/>
   </bookViews>
@@ -178,10 +178,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>title=极智嘉通过港交所上市审核,status=2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">SELECT * from news_flash where id=${ids[0]} </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -201,10 +197,6 @@
     <t>SELECT * from content_activity where content_id ='77359212'</t>
   </si>
   <si>
-    <t>address_name=曼谷</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>content</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -217,15 +209,23 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>number=2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>select * from news_flash where publish_time between '2026-05-23 00:00:00' and '2026-05-23 23:59:59'</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{"pageNo": 1,"pageSize": 10,"startTime": "2026-05-23 00:00:00","endTime": "2026-05-23 23:59:59"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>select id from news_flash where publish_time between '2026-05-23 00:00:00' and '2026-05-23 23:59:59'</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>address_name=曼谷,id=10422</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>title=巴克莱与摩根士丹利双双上调 Spotify 目标股价,status=2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{{ids}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -623,7 +623,7 @@
     <col min="8" max="8" width="95.265625" customWidth="1"/>
     <col min="9" max="9" width="13.53125" customWidth="1"/>
     <col min="10" max="10" width="17.06640625" customWidth="1"/>
-    <col min="11" max="11" width="84.6640625" customWidth="1"/>
+    <col min="11" max="11" width="96.46484375" customWidth="1"/>
     <col min="12" max="12" width="50.796875" customWidth="1"/>
     <col min="13" max="13" width="27.86328125" customWidth="1"/>
   </cols>
@@ -669,7 +669,7 @@
         <v>15</v>
       </c>
       <c r="N1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="222" x14ac:dyDescent="0.4">
@@ -730,25 +730,25 @@
         <v>25</v>
       </c>
       <c r="H3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I3" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" t="s">
+        <v>40</v>
+      </c>
+      <c r="K3" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" t="s">
         <v>45</v>
-      </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" t="s">
-        <v>43</v>
       </c>
       <c r="M3" t="s">
         <v>27</v>
       </c>
       <c r="N3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.4">
@@ -783,13 +783,13 @@
         <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L4" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="N4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.4">
@@ -800,7 +800,7 @@
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D5" t="s">
         <v>29</v>
@@ -824,13 +824,13 @@
         <v>17</v>
       </c>
       <c r="K5" t="s">
+        <v>37</v>
+      </c>
+      <c r="L5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" t="s">
         <v>38</v>
-      </c>
-      <c r="L5" t="s">
-        <v>39</v>
-      </c>
-      <c r="N5" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
